--- a/projects/P_010_Current_Market_Posture/data/excel_exports/History Grid (VXX)_v3.xlsx
+++ b/projects/P_010_Current_Market_Posture/data/excel_exports/History Grid (VXX)_v3.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="27">
   <si>
     <t>High
 Price</t>
@@ -150,10 +150,10 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" relativeIndent="0" readingOrder="0"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="13.85546875" customWidth="1"/>
@@ -477,37 +477,37 @@
       <c r="A1" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="K1" t="s">
         <v>22</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="1" t="s">
         <v>25</v>
       </c>
       <c r="M1" t="s">
@@ -519,27 +519,27 @@
       <c r="Q1" t="s">
         <v>3</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="T1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="U1" s="2" t="s">
+      <c r="U1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="V1" s="2" t="s">
+      <c r="V1" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1">
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="L2" s="2"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="L2" s="1"/>
       <c r="M2" t="s">
         <v>4</v>
       </c>
@@ -561,620 +561,688 @@
       <c r="S2" t="s">
         <v>18</v>
       </c>
-      <c r="T2" s="2"/>
-      <c r="U2" s="2"/>
-      <c r="V2" s="2"/>
+      <c r="T2" s="1"/>
+      <c r="U2" s="1"/>
+      <c r="V2" s="1"/>
     </row>
     <row r="3" ht="19.5" customHeight="1">
-      <c r="A3" s="1">
-        <v>46280</v>
+      <c r="A3" s="2">
+        <v>46286</v>
       </c>
       <c r="B3">
-        <v>-0.0609455108642578</v>
+        <v>-0.408750534057617</v>
       </c>
       <c r="C3">
-        <v>0.0126724243164063</v>
+        <v>-0.321451187133789</v>
       </c>
       <c r="D3">
-        <v>-0.04522705078125</v>
+        <v>-0.284332275390625</v>
       </c>
       <c r="E3">
-        <v>18.1000003814697</v>
+        <v>17.4799995422363</v>
       </c>
       <c r="F3">
-        <v>18.5200004577637</v>
+        <v>17.7900009155273</v>
       </c>
       <c r="G3">
-        <v>18.0799999237061</v>
+        <v>17.4699993133545</v>
       </c>
       <c r="H3">
-        <v>18.2600002288818</v>
+        <v>17.6900005340576</v>
       </c>
       <c r="I3">
-        <v>18.8750438690186</v>
+        <v>17.5303287506104</v>
       </c>
       <c r="J3">
-        <v>17.3930416107178</v>
+        <v>17.1834278106689</v>
       </c>
       <c r="K3">
-        <v>7397755</v>
+        <v>9558600</v>
       </c>
       <c r="L3">
-        <v>-0.0633333325386047</v>
+        <v>-0.0223810113966465</v>
       </c>
       <c r="M3">
-        <v>49.6212120056152</v>
+        <v>18.2506275177002</v>
       </c>
       <c r="N3">
-        <v>-16.3819198608398</v>
+        <v>-3.08563446998596</v>
       </c>
       <c r="O3" t="s">
         <v>1</v>
       </c>
       <c r="P3">
-        <v>11.7754812240601</v>
+        <v>9.49167346954346</v>
       </c>
       <c r="Q3">
-        <v>18.3706474304199</v>
+        <v>17.6460456848145</v>
       </c>
       <c r="R3">
-        <v>18.2179336547852</v>
+        <v>17.9555377960205</v>
       </c>
       <c r="S3">
-        <v>18.5231037139893</v>
+        <v>18.2347831726074</v>
       </c>
       <c r="T3">
-        <v>0.355043411254883</v>
+        <v>-0.259672164916992</v>
       </c>
       <c r="U3">
-        <v>-0.686958312988281</v>
+        <v>-0.286571502685547</v>
       </c>
       <c r="V3">
-        <v>1.48200225830078</v>
+        <v>0.346900939941406</v>
       </c>
     </row>
     <row r="4" ht="19.5" customHeight="1">
-      <c r="A4" s="1">
-        <v>46279</v>
+      <c r="A4" s="2">
+        <v>46283</v>
       </c>
       <c r="B4">
-        <v>0.215251922607422</v>
+        <v>-0.322275161743164</v>
       </c>
       <c r="C4">
-        <v>0.0833034515380859</v>
+        <v>-0.255756378173828</v>
       </c>
       <c r="D4">
-        <v>-0.0379199981689453</v>
+        <v>-0.197603225708008</v>
       </c>
       <c r="E4">
-        <v>18.6299991607666</v>
+        <v>17.7600002288818</v>
       </c>
       <c r="F4">
-        <v>18.6700000762939</v>
+        <v>17.9950008392334</v>
       </c>
       <c r="G4">
-        <v>18.1100006103516</v>
+        <v>17.7350006103516</v>
       </c>
       <c r="H4">
-        <v>18.2299995422363</v>
+        <v>17.7600002288818</v>
       </c>
       <c r="I4">
-        <v>19.0564785003662</v>
+        <v>18.4081020355225</v>
       </c>
       <c r="J4">
-        <v>18.3508701324463</v>
+        <v>17.3264503479004</v>
       </c>
       <c r="K4">
-        <v>12630500</v>
+        <v>6487600</v>
       </c>
       <c r="L4">
-        <v>-0.0750000327825546</v>
+        <v>-0.0342857725918293</v>
       </c>
       <c r="M4">
-        <v>59.3426818847656</v>
+        <v>18.8317050933838</v>
       </c>
       <c r="N4">
-        <v>13.4081201553345</v>
+        <v>-35.8007888793945</v>
       </c>
       <c r="O4" t="s">
         <v>1</v>
       </c>
       <c r="P4">
-        <v>26.4773654937744</v>
+        <v>28.5029888153076</v>
       </c>
       <c r="Q4">
-        <v>18.5652160644531</v>
+        <v>17.8235206604004</v>
       </c>
       <c r="R4">
-        <v>18.2490901947021</v>
+        <v>18.0266227722168</v>
       </c>
       <c r="S4">
-        <v>18.5871562957764</v>
+        <v>18.3270492553711</v>
       </c>
       <c r="T4">
-        <v>0.386478424072266</v>
+        <v>0.413101196289063</v>
       </c>
       <c r="U4">
-        <v>0.240869522094727</v>
+        <v>-0.408550262451172</v>
       </c>
       <c r="V4">
-        <v>0.705608367919922</v>
+        <v>1.08165168762207</v>
       </c>
     </row>
     <row r="5" ht="19.5" customHeight="1">
-      <c r="A5" s="1">
-        <v>46276</v>
+      <c r="A5" s="2">
+        <v>46282</v>
       </c>
       <c r="B5">
-        <v>0.244588851928711</v>
+        <v>-0.527917861938477</v>
       </c>
       <c r="C5">
-        <v>0.155014038085938</v>
+        <v>-0.11271858215332</v>
       </c>
       <c r="D5">
-        <v>-0.0620574951171875</v>
+        <v>-0.146955490112305</v>
       </c>
       <c r="E5">
-        <v>18.2800006866455</v>
+        <v>17.7000007629395</v>
       </c>
       <c r="F5">
-        <v>18.2800006866455</v>
+        <v>17.8549995422363</v>
       </c>
       <c r="G5">
-        <v>17.9500007629395</v>
+        <v>17.6450004577637</v>
       </c>
       <c r="H5">
-        <v>18.0699996948242</v>
+        <v>17.7299995422363</v>
       </c>
       <c r="I5">
-        <v>18.1027393341064</v>
+        <v>17.3134307861328</v>
       </c>
       <c r="J5">
-        <v>17.7810745239258</v>
+        <v>16.6591320037842</v>
       </c>
       <c r="K5">
-        <v>8366600</v>
+        <v>7263600</v>
       </c>
       <c r="L5">
-        <v>-0.0454761870205402</v>
+        <v>-0.0500000528991222</v>
       </c>
       <c r="M5">
-        <v>52.32666015625</v>
+        <v>29.3332347869873</v>
       </c>
       <c r="N5">
-        <v>18.6766242980957</v>
+        <v>3.60305976867676</v>
       </c>
       <c r="O5" t="s">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="P5">
-        <v>4.21005201339722</v>
+        <v>-32.9399757385254</v>
       </c>
       <c r="Q5">
-        <v>18.5843715667725</v>
+        <v>17.8158302307129</v>
       </c>
       <c r="R5">
-        <v>18.2951793670654</v>
+        <v>18.1246662139893</v>
       </c>
       <c r="S5">
-        <v>18.6273517608643</v>
+        <v>18.3954849243164</v>
       </c>
       <c r="T5">
-        <v>-0.177261352539063</v>
+        <v>-0.541568756103516</v>
       </c>
       <c r="U5">
-        <v>-0.168926239013672</v>
+        <v>-0.985868453979492</v>
       </c>
       <c r="V5">
-        <v>0.321664810180664</v>
+        <v>0.654298782348633</v>
       </c>
     </row>
     <row r="6" ht="19.5" customHeight="1">
-      <c r="A6" s="1">
-        <v>46275</v>
+      <c r="A6" s="2">
+        <v>46281</v>
       </c>
       <c r="B6">
-        <v>1.23842620849609</v>
+        <v>0.00558853149414063</v>
       </c>
       <c r="C6">
-        <v>0.348857879638672</v>
+        <v>0.174856185913086</v>
       </c>
       <c r="D6">
-        <v>0.0548973083496094</v>
+        <v>0.0507640838623047</v>
       </c>
       <c r="E6">
-        <v>18.7299995422363</v>
+        <v>18.0900001525879</v>
       </c>
       <c r="F6">
-        <v>18.9599990844727</v>
+        <v>18.8799991607666</v>
       </c>
       <c r="G6">
-        <v>18.5149993896484</v>
+        <v>18.0100002288818</v>
       </c>
       <c r="H6">
-        <v>18.8799991607666</v>
+        <v>18.4300003051758</v>
       </c>
       <c r="I6">
-        <v>20.4675846099854</v>
+        <v>19.1645526885986</v>
       </c>
       <c r="J6">
-        <v>19.2122268676758</v>
+        <v>17.6825523376465</v>
       </c>
       <c r="K6">
-        <v>12313200</v>
+        <v>13372600</v>
       </c>
       <c r="L6">
-        <v>-0.0554761439561844</v>
+        <v>-0.0542856864631176</v>
       </c>
       <c r="M6">
-        <v>44.0918006896973</v>
+        <v>28.3130970001221</v>
       </c>
       <c r="N6">
-        <v>-12.9978160858154</v>
+        <v>-42.9415435791016</v>
       </c>
       <c r="O6" t="s">
         <v>1</v>
       </c>
       <c r="P6">
-        <v>99.9999923706055</v>
+        <v>89.3111419677734</v>
       </c>
       <c r="Q6">
-        <v>19.1845245361328</v>
+        <v>18.3983135223389</v>
       </c>
       <c r="R6">
-        <v>18.3766136169434</v>
+        <v>18.2917785644531</v>
       </c>
       <c r="S6">
-        <v>18.7248268127441</v>
+        <v>18.5138740539551</v>
       </c>
       <c r="T6">
-        <v>1.5075855255127</v>
+        <v>0.284553527832031</v>
       </c>
       <c r="U6">
-        <v>0.697227478027344</v>
+        <v>-0.327447891235352</v>
       </c>
       <c r="V6">
-        <v>1.25535774230957</v>
+        <v>1.48200035095215</v>
       </c>
     </row>
     <row r="7" ht="19.5" customHeight="1">
-      <c r="A7" s="1">
-        <v>46274</v>
+      <c r="A7" s="2">
+        <v>46280</v>
       </c>
       <c r="B7">
-        <v>1.05138206481934</v>
+        <v>-0.0609455108642578</v>
       </c>
       <c r="C7">
-        <v>0.0760021209716797</v>
+        <v>0.0126724243164063</v>
       </c>
       <c r="D7">
-        <v>-0.187383651733398</v>
+        <v>-0.04522705078125</v>
       </c>
       <c r="E7">
-        <v>18.2099990844727</v>
+        <v>18.1000003814697</v>
       </c>
       <c r="F7">
-        <v>18.3899993896484</v>
+        <v>18.5200004577637</v>
       </c>
       <c r="G7">
-        <v>18.0499992370605</v>
+        <v>18.0799999237061</v>
       </c>
       <c r="H7">
-        <v>18.2999992370605</v>
+        <v>18.2600002288818</v>
       </c>
       <c r="I7">
-        <v>20.3643932342529</v>
+        <v>18.8750438690186</v>
       </c>
       <c r="J7">
-        <v>18.6622123718262</v>
+        <v>17.3930416107178</v>
       </c>
       <c r="K7">
-        <v>8938800</v>
+        <v>7416800</v>
       </c>
       <c r="L7">
-        <v>-0.0711904242634773</v>
+        <v>-0.0633333325386047</v>
       </c>
       <c r="M7">
-        <v>50.6789588928223</v>
+        <v>49.6212120056152</v>
       </c>
       <c r="N7">
-        <v>-8.92787837982178</v>
+        <v>-16.3819198608398</v>
       </c>
       <c r="O7" t="s">
         <v>1</v>
       </c>
       <c r="P7">
-        <v>93.9265365600586</v>
+        <v>11.7754812240601</v>
       </c>
       <c r="Q7">
-        <v>18.848991394043</v>
+        <v>18.3706474304199</v>
       </c>
       <c r="R7">
-        <v>18.2094116210938</v>
+        <v>18.2179336547852</v>
       </c>
       <c r="S7">
-        <v>18.6945819854736</v>
+        <v>18.5231037139893</v>
       </c>
       <c r="T7">
-        <v>1.97439384460449</v>
+        <v>0.355043411254883</v>
       </c>
       <c r="U7">
-        <v>0.612213134765625</v>
+        <v>-0.686958312988281</v>
       </c>
       <c r="V7">
-        <v>1.70218086242676</v>
+        <v>1.48200225830078</v>
       </c>
     </row>
     <row r="8" ht="19.5" customHeight="1">
-      <c r="A8" s="1">
-        <v>46273</v>
+      <c r="A8" s="2">
+        <v>46279</v>
       </c>
       <c r="B8">
-        <v>0.746273040771484</v>
+        <v>0.215251922607422</v>
       </c>
       <c r="C8">
-        <v>-0.185245513916016</v>
+        <v>0.0833034515380859</v>
       </c>
       <c r="D8">
-        <v>-0.446632385253906</v>
+        <v>-0.0379199981689453</v>
       </c>
       <c r="E8">
-        <v>17.6800003051758</v>
+        <v>18.6299991607666</v>
       </c>
       <c r="F8">
-        <v>18.0900001525879</v>
+        <v>18.6700000762939</v>
       </c>
       <c r="G8">
-        <v>17.6700000762939</v>
+        <v>18.1100006103516</v>
       </c>
       <c r="H8">
-        <v>17.9899997711182</v>
+        <v>18.2299995422363</v>
       </c>
       <c r="I8">
-        <v>20.4618854522705</v>
+        <v>19.0564785003662</v>
       </c>
       <c r="J8">
-        <v>18.5222759246826</v>
+        <v>18.3508701324463</v>
       </c>
       <c r="K8">
-        <v>6210500</v>
+        <v>12630500</v>
       </c>
       <c r="L8">
-        <v>-0.0769047513604164</v>
+        <v>-0.0750000327825546</v>
       </c>
       <c r="M8">
-        <v>55.6470603942871</v>
+        <v>59.3426818847656</v>
       </c>
       <c r="N8">
-        <v>-26.9746246337891</v>
+        <v>13.4081201553345</v>
       </c>
       <c r="O8" t="s">
         <v>1</v>
       </c>
       <c r="P8">
-        <v>73.5614700317383</v>
+        <v>26.4773654937744</v>
       </c>
       <c r="Q8">
-        <v>18.5894374847412</v>
+        <v>18.5652160644531</v>
       </c>
       <c r="R8">
-        <v>18.1158294677734</v>
+        <v>18.2490901947021</v>
       </c>
       <c r="S8">
-        <v>18.7007236480713</v>
+        <v>18.5871562957764</v>
       </c>
       <c r="T8">
-        <v>2.37188529968262</v>
+        <v>0.386478424072266</v>
       </c>
       <c r="U8">
-        <v>0.852275848388672</v>
+        <v>0.240869522094727</v>
       </c>
       <c r="V8">
-        <v>1.93960952758789</v>
+        <v>0.705608367919922</v>
       </c>
     </row>
     <row r="9" ht="19.5" customHeight="1">
-      <c r="A9" s="1">
-        <v>46269</v>
+      <c r="A9" s="2">
+        <v>46276</v>
       </c>
       <c r="B9">
-        <v>0.214227676391602</v>
+        <v>0.244588851928711</v>
       </c>
       <c r="C9">
-        <v>-0.452966690063477</v>
+        <v>0.155014038085938</v>
       </c>
       <c r="D9">
-        <v>-0.666421890258789</v>
+        <v>-0.0620574951171875</v>
       </c>
       <c r="E9">
-        <v>17.5</v>
+        <v>18.2800006866455</v>
       </c>
       <c r="F9">
-        <v>17.7399997711182</v>
+        <v>18.2800006866455</v>
       </c>
       <c r="G9">
-        <v>17.4150009155273</v>
+        <v>17.9500007629395</v>
       </c>
       <c r="H9">
-        <v>17.7199993133545</v>
+        <v>18.0699996948242</v>
       </c>
       <c r="I9">
-        <v>19.3586082458496</v>
+        <v>18.1027393341064</v>
       </c>
       <c r="J9">
-        <v>17.9886627197266</v>
+        <v>17.7810745239258</v>
       </c>
       <c r="K9">
-        <v>5458600</v>
+        <v>8366600</v>
       </c>
       <c r="L9">
-        <v>-0.0888095125555992</v>
+        <v>-0.0454761870205402</v>
       </c>
       <c r="M9">
-        <v>76.2023620605469</v>
+        <v>52.32666015625</v>
       </c>
       <c r="N9">
-        <v>-12.0565433502197</v>
+        <v>18.6766242980957</v>
       </c>
       <c r="O9" t="s">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="P9">
-        <v>-3.28855419158936</v>
+        <v>4.21005201339722</v>
       </c>
       <c r="Q9">
-        <v>18.1873207092285</v>
+        <v>18.5843715667725</v>
       </c>
       <c r="R9">
-        <v>18.0886688232422</v>
+        <v>18.2951793670654</v>
       </c>
       <c r="S9">
-        <v>18.7417659759521</v>
+        <v>18.6273517608643</v>
       </c>
       <c r="T9">
-        <v>1.61860847473145</v>
+        <v>-0.177261352539063</v>
       </c>
       <c r="U9">
-        <v>0.573661804199219</v>
+        <v>-0.168926239013672</v>
       </c>
       <c r="V9">
-        <v>1.36994552612305</v>
+        <v>0.321664810180664</v>
       </c>
     </row>
     <row r="10" ht="19.5" customHeight="1">
-      <c r="A10" s="1">
-        <v>46268</v>
+      <c r="A10" s="2">
+        <v>46275</v>
       </c>
       <c r="B10">
-        <v>-0.232887268066406</v>
+        <v>1.23842620849609</v>
       </c>
       <c r="C10">
-        <v>-0.477483749389648</v>
+        <v>0.348857879638672</v>
       </c>
       <c r="D10">
-        <v>-0.682571411132813</v>
+        <v>0.0548973083496094</v>
       </c>
       <c r="E10">
-        <v>17.8999996185303</v>
+        <v>18.7299995422363</v>
       </c>
       <c r="F10">
-        <v>18</v>
+        <v>18.9599990844727</v>
       </c>
       <c r="G10">
-        <v>17.6200008392334</v>
+        <v>18.5149993896484</v>
       </c>
       <c r="H10">
-        <v>17.6200008392334</v>
+        <v>18.8799991607666</v>
       </c>
       <c r="I10">
-        <v>18.074426651001</v>
+        <v>20.4675846099854</v>
       </c>
       <c r="J10">
-        <v>17.3740425109863</v>
+        <v>19.2122268676758</v>
       </c>
       <c r="K10">
-        <v>9171100</v>
+        <v>12313200</v>
       </c>
       <c r="L10">
-        <v>-0.121666684746742</v>
+        <v>-0.0554761439561844</v>
       </c>
       <c r="M10">
-        <v>86.6492691040039</v>
+        <v>44.0918006896973</v>
       </c>
       <c r="N10">
-        <v>21.1536731719971</v>
+        <v>-12.9978160858154</v>
       </c>
       <c r="O10" t="s">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="P10">
-        <v>-33.7902526855469</v>
+        <v>99.9999923706055</v>
       </c>
       <c r="Q10">
-        <v>18.0195541381836</v>
+        <v>19.1845245361328</v>
       </c>
       <c r="R10">
-        <v>18.2159900665283</v>
+        <v>18.3766136169434</v>
       </c>
       <c r="S10">
-        <v>18.8685245513916</v>
+        <v>18.7248268127441</v>
       </c>
       <c r="T10">
-        <v>0.0744266510009766</v>
+        <v>1.5075855255127</v>
       </c>
       <c r="U10">
-        <v>-0.24595832824707</v>
+        <v>0.697227478027344</v>
       </c>
       <c r="V10">
-        <v>0.700384140014648</v>
+        <v>1.25535774230957</v>
       </c>
     </row>
     <row r="11" ht="19.5" customHeight="1">
-      <c r="A11" s="1">
-        <v>46267</v>
+      <c r="A11" s="2">
+        <v>46274</v>
       </c>
       <c r="B11">
-        <v>0.0465126037597656</v>
+        <v>1.05138206481934</v>
       </c>
       <c r="C11">
-        <v>-0.385969161987305</v>
+        <v>0.0760021209716797</v>
       </c>
       <c r="D11">
-        <v>-0.555747985839844</v>
+        <v>-0.187383651733398</v>
       </c>
       <c r="E11">
-        <v>18.4300003051758</v>
+        <v>18.2099990844727</v>
       </c>
       <c r="F11">
-        <v>18.4799995422363</v>
+        <v>18.3899993896484</v>
       </c>
       <c r="G11">
-        <v>17.9799995422363</v>
+        <v>18.0499992370605</v>
       </c>
       <c r="H11">
-        <v>18.0200004577637</v>
+        <v>18.2999992370605</v>
       </c>
       <c r="I11">
-        <v>18.2182636260986</v>
+        <v>20.3643932342529</v>
       </c>
       <c r="J11">
-        <v>17.7632369995117</v>
+        <v>18.6622123718262</v>
       </c>
       <c r="K11">
-        <v>7431600</v>
+        <v>8938800</v>
       </c>
       <c r="L11">
-        <v>-0.147857218980789</v>
+        <v>-0.0711904242634773</v>
       </c>
       <c r="M11">
-        <v>71.520133972168</v>
+        <v>50.6789588928223</v>
       </c>
       <c r="N11">
-        <v>15.156270980835</v>
+        <v>-8.92787837982178</v>
       </c>
       <c r="O11" t="s">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="P11">
-        <v>-0.0907894745469093</v>
+        <v>93.9265365600586</v>
       </c>
       <c r="Q11">
-        <v>18.3491058349609</v>
+        <v>18.848991394043</v>
       </c>
       <c r="R11">
-        <v>18.4079036712646</v>
+        <v>18.2094116210938</v>
       </c>
       <c r="S11">
-        <v>19.0530338287354</v>
+        <v>18.6945819854736</v>
       </c>
       <c r="T11">
-        <v>-0.261735916137695</v>
+        <v>1.97439384460449</v>
       </c>
       <c r="U11">
-        <v>-0.216762542724609</v>
+        <v>0.612213134765625</v>
       </c>
       <c r="V11">
-        <v>0.455026626586914</v>
+        <v>1.70218086242676</v>
+      </c>
+    </row>
+    <row r="12" ht="19.5" customHeight="1">
+      <c r="A12" s="2">
+        <v>46273</v>
+      </c>
+      <c r="B12">
+        <v>0.746273040771484</v>
+      </c>
+      <c r="C12">
+        <v>-0.185245513916016</v>
+      </c>
+      <c r="D12">
+        <v>-0.446632385253906</v>
+      </c>
+      <c r="E12">
+        <v>17.6800003051758</v>
+      </c>
+      <c r="F12">
+        <v>18.0900001525879</v>
+      </c>
+      <c r="G12">
+        <v>17.6700000762939</v>
+      </c>
+      <c r="H12">
+        <v>17.9899997711182</v>
+      </c>
+      <c r="I12">
+        <v>20.4618854522705</v>
+      </c>
+      <c r="J12">
+        <v>18.5222759246826</v>
+      </c>
+      <c r="K12">
+        <v>6210500</v>
+      </c>
+      <c r="L12">
+        <v>-0.0769047513604164</v>
+      </c>
+      <c r="M12">
+        <v>55.6470603942871</v>
+      </c>
+      <c r="N12">
+        <v>-26.9746246337891</v>
+      </c>
+      <c r="O12" t="s">
+        <v>1</v>
+      </c>
+      <c r="P12">
+        <v>73.5614700317383</v>
+      </c>
+      <c r="Q12">
+        <v>18.5894374847412</v>
+      </c>
+      <c r="R12">
+        <v>18.1158294677734</v>
+      </c>
+      <c r="S12">
+        <v>18.7007236480713</v>
+      </c>
+      <c r="T12">
+        <v>2.37188529968262</v>
+      </c>
+      <c r="U12">
+        <v>0.852275848388672</v>
+      </c>
+      <c r="V12">
+        <v>1.93960952758789</v>
       </c>
     </row>
   </sheetData>
